--- a/output/pdf_financials_xlsx/KNE.xlsx
+++ b/output/pdf_financials_xlsx/KNE.xlsx
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.8049190000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.8049190000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.319386</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.415015</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.634442</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.966166</v>
@@ -2427,19 +2427,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.8049190000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.8049190000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.319386</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.415015</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.634442</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.966166</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.81625</v>
+        <v>0.011331</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.011331</v>
@@ -20242,7 +20242,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">

--- a/output/pdf_financials_xlsx/KNE.xlsx
+++ b/output/pdf_financials_xlsx/KNE.xlsx
@@ -1070,25 +1070,25 @@
         <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>0.004476</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.09188</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.114226</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.09121600000000001</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.082167</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.038582</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>-0</v>
@@ -1976,25 +1976,25 @@
         <v>-1.472296</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.43643</v>
+        <v>-1.440906</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.608038</v>
+        <v>-1.516158</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-1.704751</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.539361</v>
+        <v>-2.425135</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.385118</v>
+        <v>-3.293902</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.251379</v>
+        <v>-3.169212</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.959724</v>
+        <v>-0.921142</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-4.727983</v>
@@ -2022,49 +2022,49 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.011047</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.008142999999999999</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.008984000000000001</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.00988</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.029551</v>
+        <v>0.039243</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.032527</v>
+        <v>0.042556</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.035255</v>
+        <v>0.048984</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.053305</v>
+        <v>0.069385</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.057422</v>
+        <v>0.071781</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.038979</v>
+        <v>0.054424</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.048982</v>
+        <v>0.18797</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.07718999999999999</v>
+        <v>0.267542</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.072062</v>
+        <v>0.244066</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.057344</v>
+        <v>0.21847</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.031596</v>
+        <v>0.162738</v>
       </c>
     </row>
     <row r="29">
@@ -2077,49 +2077,49 @@
         <v>-0.877247</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.97992</v>
+        <v>-0.968873</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.241337</v>
+        <v>-1.233194</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.472296</v>
+        <v>-1.463312</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.43643</v>
+        <v>-1.431026</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.578487</v>
+        <v>-1.476915</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.672224</v>
+        <v>-1.662195</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.504106</v>
+        <v>-2.376151</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.331813</v>
+        <v>-3.224517</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.193957</v>
+        <v>-3.097431</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.920745</v>
+        <v>-0.866718</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.679001</v>
+        <v>-4.540013</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.731347</v>
+        <v>-3.540995</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.192326</v>
+        <v>-5.020322</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.218658</v>
+        <v>6.379784</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.708637</v>
+        <v>-2.577495</v>
       </c>
     </row>
     <row r="30">
@@ -2149,40 +2149,40 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-898.0774641282942</v>
+        <v>-894.6988027134328</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-3767.36198954629</v>
+        <v>-3524.940929377789</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-1598.317785594127</v>
+        <v>-1588.732030891574</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-659.166074389955</v>
+        <v>-625.4839558819658</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-792.4001893115102</v>
+        <v>-766.8821393151966</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-630.8764243797319</v>
+        <v>-611.8104263905047</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-54.36858290759387</v>
+        <v>-51.17837125426035</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-291.0233708074824</v>
+        <v>-282.3786288504299</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-2380.702851345919</v>
+        <v>-2259.252997135256</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-3485.250369177071</v>
+        <v>-3369.795945764532</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>298.8476504400304</v>
+        <v>306.5908205138309</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-633.0528736599287</v>
+        <v>-602.4028382518949</v>
       </c>
     </row>
     <row r="31">
@@ -6006,49 +6006,49 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.011047</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.008142999999999999</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.008984000000000001</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.00988</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.039243</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.042556</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.048984</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.069385</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.071781</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.054424</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.18797</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.267542</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.244066</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.21847</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.162738</v>
       </c>
     </row>
     <row r="101">
@@ -24850,7 +24850,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -24946,7 +24950,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -27838,7 +27842,11 @@
           <t>Additions to intangible assets 11</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -29348,7 +29356,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -29444,7 +29456,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -29540,7 +29552,11 @@
           <t>Derecognition of property and equipment 10</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -32574,7 +32590,11 @@
           <t>Depreciation of property and equipment 5,9</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -32670,7 +32690,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -32766,7 +32786,11 @@
           <t>Derecognition of property and equipment 9</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -34550,7 +34574,11 @@
           <t>Additions to intangible assets 5,10</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -35284,7 +35312,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -35380,7 +35412,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -35476,7 +35508,11 @@
           <t>Derecognition of property and equipment 8</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -37376,7 +37412,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -37828,7 +37868,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -37922,7 +37966,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -39734,7 +39778,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -41058,7 +41106,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -41154,7 +41206,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -42410,7 +42462,11 @@
           <t>Additions to intangible assets 7</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -42978,7 +43034,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -43064,7 +43124,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -44084,7 +44144,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -62384,7 +62448,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E577" t="inlineStr">
         <is>
           <t>-</t>
